--- a/output/pdf_financials_xlsx/CMU.xlsx
+++ b/output/pdf_financials_xlsx/CMU.xlsx
@@ -5095,46 +5095,46 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.505255</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.505255</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.505255</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.505255</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.607258</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.607258</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.607258</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.607258</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.5411859999999999</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.5411859999999999</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.5411859999999999</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.803068</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.844619</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.974938</v>
       </c>
     </row>
     <row r="93">
@@ -9282,7 +9282,11 @@
           <t>Share based payment reserve 13</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -11244,7 +11248,11 @@
           <t>Share based payment reserve 16</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -12024,7 +12032,11 @@
           <t>Share based payment reserve 14</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -13144,7 +13156,11 @@
           <t>SHARE BASED PAYMENT RESERVE</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -14816,7 +14832,11 @@
           <t>SHARE BASED PAYMENT RESERVE</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E87" s="5" t="n">
         <v>0.505255</v>
       </c>

--- a/output/pdf_financials_xlsx/CMU.xlsx
+++ b/output/pdf_financials_xlsx/CMU.xlsx
@@ -1016,13 +1016,13 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.074999</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.298191</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.053699</v>
       </c>
     </row>
     <row r="13">
@@ -1807,13 +1807,13 @@
         <v>-0.121144</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>9.209775</v>
+        <v>9.134776</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.482039</v>
+        <v>-0.78023</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.732545</v>
+        <v>-0.7862440000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1905,13 +1905,13 @@
         <v>-0.121144</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>9.210274999999999</v>
+        <v>9.135275999999999</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.47649</v>
+        <v>-0.774681</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.718451</v>
+        <v>-0.77215</v>
       </c>
     </row>
     <row r="30">
@@ -2123,34 +2123,34 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.023836</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.037542</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.354115</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.254374</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.056954</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.07206600000000001</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.057507</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.07040100000000001</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.311358</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.826703</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>0.73098</v>
@@ -2221,34 +2221,34 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.023836</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.037542</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.354115</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.254374</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.056954</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.07206600000000001</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.057507</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.07040100000000001</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.311358</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.826703</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>0.73098</v>
@@ -2809,34 +2809,34 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.023836</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.044822</v>
+        <v>0.00728</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.388317</v>
+        <v>0.034202</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.287486</v>
+        <v>0.033112</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.094748</v>
+        <v>0.037794</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.106098</v>
+        <v>0.034032</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.093283</v>
+        <v>0.035776</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.094622</v>
+        <v>0.024221</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.335579</v>
+        <v>0.024221</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.850523</v>
+        <v>0.02382</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0.02732</v>
@@ -12206,7 +12206,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -16600,7 +16600,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
@@ -23540,7 +23540,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">

--- a/output/pdf_financials_xlsx/CMU.xlsx
+++ b/output/pdf_financials_xlsx/CMU.xlsx
@@ -738,19 +738,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.170465</v>
+        <v>0.176465</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.133574</v>
+        <v>0.144074</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.128413</v>
+        <v>0.134413</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.148448</v>
+        <v>0.154448</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.140661</v>
+        <v>0.146161</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0.139147</v>
@@ -19844,7 +19844,11 @@
           <t>Proceeds from shares issued 12</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -21138,7 +21142,11 @@
           <t>Proceeds from shares issued</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E163" s="5" t="n">
         <v>0.175</v>
       </c>
@@ -32832,7 +32840,11 @@
           <t>Directors fees 5</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr">
         <is>
           <t>-</t>
@@ -34558,7 +34570,11 @@
           <t>Directors fees (Note 5)</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
@@ -36100,7 +36116,11 @@
           <t>Directors fees</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E340" s="5" t="n">
         <v>0.006</v>
       </c>
